--- a/out/final/intraday_main_table.xlsx
+++ b/out/final/intraday_main_table.xlsx
@@ -1,34 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t>N_events</t>
+  </si>
+  <si>
+    <t>mean_CAR</t>
+  </si>
+  <si>
+    <t>median_CAR</t>
+  </si>
+  <si>
+    <t>std_CAR</t>
+  </si>
+  <si>
+    <t>t_stat</t>
+  </si>
+  <si>
+    <t>t_pvalue</t>
+  </si>
+  <si>
+    <t>wilcoxon_stat</t>
+  </si>
+  <si>
+    <t>wilcoxon_pvalue</t>
+  </si>
+  <si>
+    <t>sign_test_pvalue</t>
+  </si>
+  <si>
+    <t>share_positive</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>p25</t>
+  </si>
+  <si>
+    <t>p50</t>
+  </si>
+  <si>
+    <t>p75</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>main_sample</t>
+  </si>
+  <si>
+    <t>raw_simple</t>
+  </si>
+  <si>
+    <t>[-1;1]</t>
+  </si>
+  <si>
+    <t>[-2;2]</t>
+  </si>
+  <si>
+    <t>[-4;0]_pre</t>
+  </si>
+  <si>
+    <t>[0;2]</t>
+  </si>
+  <si>
+    <t>[0;4]</t>
+  </si>
+  <si>
+    <t>[0;close_D0]</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +128,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,417 +422,403 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>N_events</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>mean_CAR</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>median_CAR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>std_CAR</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>t_stat</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>t_pvalue</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>wilcoxon_stat</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>wilcoxon_pvalue</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>sign_test_pvalue</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>share_positive</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>p25</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>p50</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>p75</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>main_sample</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>raw_simple</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[-1;1]</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
         <v>22</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.004943566338022867</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.0009330340229199985</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.01586593704859292</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>1.461456792030537</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.1586932230954308</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>75</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.09841060638427734</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.2862787246704102</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.6363636363636364</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>-0.0192384373042882</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>-0.0008090113797638299</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>0.0009330340229199985</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>0.004205790284334765</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>0.06007526025259757</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>main_sample</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>raw_simple</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[-2;2]</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
         <v>22</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.003272799419570013</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.0008919509622756783</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.012890541058831</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>1.190856916419013</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.2469969157865985</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>85</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.186976432800293</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.2862787246704102</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.6363636363636364</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>-0.02752185624303993</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>-0.001437447350928961</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>0.0008919509622756783</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>0.007775640842962339</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>0.03272059471286926</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>main_sample</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>raw_simple</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[0;2]</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>0.002571247199382141</v>
+      </c>
+      <c r="F4">
+        <v>0.001020545590383615</v>
+      </c>
+      <c r="G4">
+        <v>0.007099265192702761</v>
+      </c>
+      <c r="H4">
+        <v>1.698798123329776</v>
+      </c>
+      <c r="I4">
+        <v>0.1041256824854808</v>
+      </c>
+      <c r="J4">
+        <v>77</v>
+      </c>
+      <c r="K4">
+        <v>0.1128716468811035</v>
+      </c>
+      <c r="L4">
+        <v>0.5234670639038086</v>
+      </c>
+      <c r="M4">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="N4">
+        <v>-0.009145388429891765</v>
+      </c>
+      <c r="O4">
+        <v>-0.0009746372528877389</v>
+      </c>
+      <c r="P4">
+        <v>0.001020545590383615</v>
+      </c>
+      <c r="Q4">
+        <v>0.00372145495705975</v>
+      </c>
+      <c r="R4">
+        <v>0.02168665272178383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
         <v>0.001921544789455756</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5">
         <v>0.000430938521319979</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5">
         <v>0.0118054671771176</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5">
         <v>0.7634466157459112</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5">
         <v>0.4536892745038096</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5">
         <v>96</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5">
         <v>0.3369474411010742</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L5">
         <v>0.5234670639038086</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5">
         <v>0.5909090909090909</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N5">
         <v>-0.0254092992069801</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O5">
         <v>-0.0005320861364266072</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P5">
         <v>0.000430938521319979</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q5">
         <v>0.002562012098892397</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R5">
         <v>0.0384169102315739</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>main_sample</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>raw_simple</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[0;4]</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
         <v>22</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6">
         <v>0.002850879050477343</v>
       </c>
-      <c r="F5" t="n">
-        <v>2.064002913826357e-05</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F6">
+        <v>2.064002913826357E-05</v>
+      </c>
+      <c r="G6">
         <v>0.01265582160271156</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6">
         <v>1.056573681857558</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6">
         <v>0.3027101230687341</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6">
         <v>112</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6">
         <v>0.6556386947631836</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6">
         <v>0.5</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N6">
         <v>-0.02078052009643994</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O6">
         <v>-0.001592125915147624</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.064002913826357e-05</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="P6">
+        <v>2.064002913826357E-05</v>
+      </c>
+      <c r="Q6">
         <v>0.003517250008865047</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6">
         <v>0.0375556823089499</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>main_sample</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>raw_simple</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[0;close_D0]</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
         <v>22</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7">
         <v>0.005388822501216573</v>
       </c>
-      <c r="F6" t="n">
-        <v>-5.726044463105762e-05</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F7">
+        <v>-5.726044463105762E-05</v>
+      </c>
+      <c r="G7">
         <v>0.02634365805208292</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7">
         <v>0.9594650043143432</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7">
         <v>0.3482419932599468</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7">
         <v>123</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7">
         <v>0.9239659309387207</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7">
         <v>0.5</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N7">
         <v>-0.02625351548000199</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O7">
         <v>-0.008770509727930753</v>
       </c>
-      <c r="P6" t="n">
-        <v>-5.726044463105762e-05</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="P7">
+        <v>-5.726044463105762E-05</v>
+      </c>
+      <c r="Q7">
         <v>0.004991462011066511</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7">
         <v>0.07737662273893053</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>